--- a/Result/profitability/8923.xlsx
+++ b/Result/profitability/8923.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2325</v>
+        <v>0.24125</v>
       </c>
       <c r="N2" t="n">
-        <v>45.55625000000001</v>
+        <v>44.41875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.235</v>
+        <v>0.21875</v>
       </c>
       <c r="N3" t="n">
-        <v>45.53125</v>
+        <v>44.55125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2175</v>
+        <v>0.1825</v>
       </c>
       <c r="N4" t="n">
-        <v>45.5275</v>
+        <v>44.58125</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2075</v>
+        <v>0.22625</v>
       </c>
       <c r="N5" t="n">
-        <v>46.1475</v>
+        <v>45.295</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23875</v>
+        <v>0.25625</v>
       </c>
       <c r="N6" t="n">
-        <v>46.28375</v>
+        <v>45.815</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2575</v>
+        <v>0.2375</v>
       </c>
       <c r="N7" t="n">
-        <v>47.485</v>
+        <v>46.35625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2375</v>
+        <v>0.24</v>
       </c>
       <c r="N8" t="n">
-        <v>47.465</v>
+        <v>46.715</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.26625</v>
       </c>
       <c r="N9" t="n">
-        <v>48.39750000000001</v>
+        <v>48.3975</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.31125</v>
       </c>
       <c r="N11" t="n">
-        <v>48.43875000000001</v>
+        <v>48.43875</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
         <v>0.26</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="N12" t="n">
-        <v>48.63125</v>
+        <v>48.63124999999999</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8923</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>125</v>
+      </c>
+      <c r="D75" t="n">
+        <v>78</v>
+      </c>
+      <c r="E75" t="n">
+        <v>47</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.20%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.22375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.79375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1111111111111112</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1378359751895245</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1537767756482525</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
